--- a/reports/tables/comparativa_final.xlsx
+++ b/reports/tables/comparativa_final.xlsx
@@ -562,22 +562,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7028</v>
+        <v>0.6489</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>0.8199</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>-0.002</v>
+        <v>0.9091</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.0851</v>
       </c>
       <c r="E5" t="n">
-        <v>0.481</v>
+        <v>0.4379</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.6063</v>
+        <v>0.591</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>0.8064</v>
+        <v>0.8131</v>
       </c>
     </row>
   </sheetData>
